--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/17_managed_services_scope.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/17_managed_services_scope.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rbb399bc09a154efa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R8c0fddb11abd4263"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rc5d43b306da44dc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Ra05bb616d10f40d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rde657a97988641d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R93f80192f64f49bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R221833c092cc451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R44eb46d75ae64f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R2280ab8a126043df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R6afb090f5cb2477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R7c46fab0681a41f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R451416cc65e14bc1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -674,7 +674,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fb4d6b9e82a42ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfceebfe18f924442"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -845,7 +845,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N6" s="81" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Executive Office support and managed service scope (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for managed services scope.</x:v>
       </x:c>
       <x:c r="O6" s="82" t="str">
         <x:v>Medium</x:v>
@@ -892,7 +892,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N7" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm Provider Operations support and managed service scope (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this managed services scope record is used downstream.</x:v>
       </x:c>
       <x:c r="O7" t="str">
         <x:v>Medium</x:v>
@@ -939,7 +939,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Attach client evidence for Claims Operations support and managed service scope (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O8" t="str">
         <x:v>Medium</x:v>
@@ -986,7 +986,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Reconcile Eligibility and Benefits support and managed service scope (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O9" t="str">
         <x:v>Medium</x:v>
@@ -1033,7 +1033,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization and UM support and managed service scope (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O10" t="str">
         <x:v>Medium</x:v>
@@ -1080,7 +1080,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Contact Center and Member Service support and managed service scope (record 6) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O11" t="str">
         <x:v>Medium</x:v>
@@ -1127,7 +1127,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm Revenue Cycle Operations support and managed service scope (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this managed services scope record is used downstream.</x:v>
       </x:c>
       <x:c r="O12" t="str">
         <x:v>Medium</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Finance Analytics support and managed service scope (record 8) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O13" t="str">
         <x:v>Medium</x:v>
@@ -1221,7 +1221,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Reconcile Workforce Analytics support and managed service scope (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O14" t="str">
         <x:v>Medium</x:v>
@@ -1268,7 +1268,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics support and managed service scope (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O15" t="str">
         <x:v>Medium</x:v>
@@ -1315,7 +1315,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Claims and Payment Analytics support and managed service scope (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for managed services scope.</x:v>
       </x:c>
       <x:c r="O16" t="str">
         <x:v>Medium</x:v>
@@ -1362,7 +1362,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm Provider Performance Analytics support and managed service scope (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this managed services scope record is used downstream.</x:v>
       </x:c>
       <x:c r="O17" t="str">
         <x:v>Medium</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Attach client evidence for Enterprise Data Platform support and managed service scope (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O18" t="str">
         <x:v>Medium</x:v>
@@ -1456,7 +1456,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Reconcile Data Governance and Data Quality support and managed service scope (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O19" t="str">
         <x:v>Medium</x:v>
@@ -1503,7 +1503,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action support and managed service scope (record 15) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O20" t="str">
         <x:v>Medium</x:v>
@@ -1550,7 +1550,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Validate Unified Clinical and Claims Lakehouse support and managed service scope (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for managed services scope.</x:v>
       </x:c>
       <x:c r="O21" t="str">
         <x:v>Medium</x:v>
@@ -1597,7 +1597,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline support and managed service scope (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this managed services scope record is used downstream.</x:v>
       </x:c>
       <x:c r="O22" t="str">
         <x:v>Medium</x:v>
@@ -1644,7 +1644,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization support and managed service scope (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O23" t="str">
         <x:v>Medium</x:v>
@@ -1691,7 +1691,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Reconcile Infrastructure and CMDB support and managed service scope (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O24" t="str">
         <x:v>Medium</x:v>
@@ -1738,7 +1738,7 @@
         <x:v>Potential scope rationalization, automation, SLA tightening, knowledge transition, vendor consolidation; no realized savings claim.</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>Need contract, ticket history, SLA performance, resource model, and transition constraints.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations support and managed service scope (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O25" t="str">
         <x:v>Medium</x:v>
@@ -1759,7 +1759,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd13208e04640474c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79438b59505f41a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1834,7 +1834,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc121d9dd85804967"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68016b8b13dd4ded"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1971,7 +1971,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b398742348c4a40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a202b7d0ae949a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2033,7 +2033,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e2c42426ef24015"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf293a0e3e5ee42d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2143,7 +2143,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R896d967ee2334d68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10686e16a36c44df"/>
   </x:tableParts>
 </x:worksheet>
 </file>